--- a/i18n/template.xlsx
+++ b/i18n/template.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="1024">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -3092,6 +3092,15 @@
   </si>
   <si>
     <t xml:space="preserve">Show bonus cards match symbols</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official ruling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applies to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show less</t>
   </si>
 </sst>
 </file>
@@ -11572,7 +11581,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.88"/>
@@ -11660,8 +11669,22 @@
       <c r="B13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>1021</v>
+      </c>
       <c r="B14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B16" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
